--- a/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
+++ b/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-347872</t>
+          <t>I-57514</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-11.1235539</t>
+          <t>-11.1073856</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-77.6103328</t>
+          <t>-77.602619</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Túpac Amaru / Jirón Augusto B Leguia</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-347877</t>
+          <t>I-57742</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-11.1236352</t>
+          <t>-11.1075587</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-77.6101412</t>
+          <t>-77.6100368</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida 28 de Julio / Avenida Echenique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-347878</t>
+          <t>I-57766</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,22 +612,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-11.1236578</t>
+          <t>-11.1072713</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-77.6103195</t>
+          <t>-77.6062456</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida 28 de Julio / Calle Domingo Coloma</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -639,12 +639,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-347879</t>
+          <t>I-191372</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150801</t>
+          <t>150810</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -659,27 +659,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HUACHO</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-11.1236766</t>
+          <t>-11.1042363</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-77.6104679</t>
+          <t>-77.5755234</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Mercedes Indacochea Lozano / Calle Alameda del Recuerdo</t>
+          <t>Avenida El Milagro / Avenida Libertad</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-497631</t>
+          <t>I-493573</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150801</t>
+          <t>150810</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,27 +711,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HUACHO</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-11.1022696</t>
+          <t>-11.0938372</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-77.597746</t>
+          <t>-77.581623</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle Andrés Avelino Cáceres / Calle Progreso</t>
+          <t>Avenida 28 de Julio / Avenida San Martin</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-57515</t>
+          <t>I-267961</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150801</t>
+          <t>150811</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -763,27 +763,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HUACHO</t>
+          <t>SAYAN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-11.1073919</t>
+          <t>-11.149087</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-77.5988002</t>
+          <t>-77.24483</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida La Paz / Avenida Túpac Amaru</t>
+          <t>Andahuasi / Sayan</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-57700</t>
+          <t>I-445312</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,22 +820,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-11.1069931</t>
+          <t>-11.12715</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-77.5987245</t>
+          <t>-77.6113995</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida La Paz / Pasaje Túpac Amaru</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,12 +847,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-796307</t>
+          <t>I-439875</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150801</t>
+          <t>150811</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -867,30 +867,654 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>SAYAN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-11.2180889</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-77.409188</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Avenida Principal / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-439878</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>150811</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SAYAN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-11.216606</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-77.412813</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Irrigacion Santa Rosa / 9 De Octubre - Sayan</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-439880</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>150811</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SAYAN</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-11.214964</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-77.41671</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Irrigacion Sta Rosa / 9 De Octubre - Sayan</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-594257</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>150810</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-11.0938163</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-77.5839428</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Avenida San Martin / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-497614</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>150810</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-11.0870753</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-77.5718196</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Avenida Libertad / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-439518</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>150811</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SAYAN</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-11.1974513</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-77.4244146</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-57732</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>HUACHO</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-11.1235415</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-77.6102476</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-11.127642</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-77.614519</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Jose Galvez / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-57390</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-11.1299197</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-77.6109194</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-498231</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-11.1251544</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-77.6022257</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-57895</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>150805</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HUALMAY</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-11.1007134</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-77.6211552</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>José Olaya / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-57893</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>150805</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HUALMAY</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-11.1017444</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-77.6202001</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>José Olaya / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-57892</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>150805</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HUALMAY</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-11.1034042</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-77.6157061</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Jose Olaya / José Olaya</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-88612</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>150811</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SAYAN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-11.2342322</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-77.3984911</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>150801</t>
         </is>

--- a/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
+++ b/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,7 +570,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida 28 de Julio / Avenida Echenique</t>
+          <t>Avenida 28 de Julio / Avenida Echenique / Jirón Atahualpa</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Irrigacion Santa Rosa / 9 De Octubre - Sayan</t>
+          <t>Avenida Principal / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Irrigacion Sta Rosa / 9 De Octubre - Sayan</t>
+          <t>Avenida Principal / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Jose Olaya / José Olaya</t>
+          <t>Jose Olaya / José Olaya / Pasaje Campo Alegre</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1515,6 +1515,214 @@
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-88618</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>150811</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SAYAN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-11.243499</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-77.4225565</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-551253</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>150811</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SAYAN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-11.1053899</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-77.3152006</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-551201</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>150811</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SAYAN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-11.1086151</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-77.3327369</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>150801</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-551203</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>150811</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SAYAN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-11.108692</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-77.3324512</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>150801</t>
         </is>

--- a/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
+++ b/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-57514</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>150801</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>HUACHO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-11.1073856</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-57742</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>150801</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HUACHO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-11.1075587</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-57766</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>150801</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HUACHO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-11.1072713</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-191372</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>150810</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SANTA MARIA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-11.1042363</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-493573</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>150810</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SANTA MARIA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-11.0938372</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-267961</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>150811</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SAYAN</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-11.149087</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-445312</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>150801</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HUACHO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-11.12715</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-439875</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>150811</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SAYAN</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-11.2180889</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-439878</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>150811</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>SAYAN</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-11.216606</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-439880</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>150811</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SAYAN</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-11.214964</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-594257</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>150810</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SANTA MARIA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-11.0938163</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-497614</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>150810</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SANTA MARIA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-11.0870753</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-439518</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>150811</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SAYAN</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-11.1974513</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-57732</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>150801</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>HUACHO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-11.127642</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-57390</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>150801</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>HUACHO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-11.1299197</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-498231</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>150801</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>HUACHO</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-11.1251544</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-57895</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>150805</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>HUALMAY</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-11.1007134</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-57893</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>150805</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>HUALMAY</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-11.1017444</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-57892</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>150805</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>HUALMAY</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-11.1034042</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-88612</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>150811</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>SAYAN</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-11.2342322</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-88618</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>150811</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>SAYAN</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-11.243499</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-551253</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>150811</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>SAYAN</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-11.1053899</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-551201</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>150811</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>SAYAN</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-11.1086151</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>150801</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HUACHO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-551203</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>150811</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>HUAURA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>SAYAN</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-11.108692</t>
@@ -1720,11 +1600,6 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>150801</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
+++ b/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
+++ b/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
+++ b/Intersecciones/excels/LIMA-HUAURA-HUACHO.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-57514</t>
+          <t>I-88618</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-11.1073856</t>
+          <t>-11.243499</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-77.602619</t>
+          <t>-77.4225565</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Jirón Augusto B Leguia</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-57742</t>
+          <t>I-88612</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-11.1075587</t>
+          <t>-11.2342322</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-77.6100368</t>
+          <t>-77.3984911</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida 28 de Julio / Avenida Echenique / Jirón Atahualpa</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-57766</t>
+          <t>I-594257</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-11.1072713</t>
+          <t>-11.0938163</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-77.6062456</t>
+          <t>-77.5839428</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida 28 de Julio / Calle Domingo Coloma</t>
+          <t>Avenida San Martin / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-191372</t>
+          <t>I-57895</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-11.1042363</t>
+          <t>-11.1007134</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-77.5755234</t>
+          <t>-77.6211552</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida El Milagro / Avenida Libertad</t>
+          <t>José Olaya / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-493573</t>
+          <t>I-57893</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-11.0938372</t>
+          <t>-11.1017444</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-77.581623</t>
+          <t>-77.6202001</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida 28 de Julio / Avenida San Martin</t>
+          <t>José Olaya / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-267961</t>
+          <t>I-57892</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-11.149087</t>
+          <t>-11.1034042</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-77.24483</t>
+          <t>-77.6157061</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Andahuasi / Sayan</t>
+          <t>Jose Olaya / José Olaya</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-445312</t>
+          <t>I-57766</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-11.12715</t>
+          <t>-11.1072713</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-77.6113995</t>
+          <t>-77.6062456</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida 28 de Julio / Calle Domingo Coloma</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,27 +815,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-439875</t>
+          <t>I-57742</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-11.2180889</t>
+          <t>-11.1075587</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-77.409188</t>
+          <t>-77.6100368</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Principal / Calle s / n</t>
+          <t>Avenida 28 de Julio / Avenida Echenique</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-439878</t>
+          <t>I-57732</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-11.216606</t>
+          <t>-11.127642</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-77.412813</t>
+          <t>-77.614519</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Principal / Calle s / n</t>
+          <t>Jose Galvez / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-439880</t>
+          <t>I-57514</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-11.214964</t>
+          <t>-11.1073856</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-77.41671</t>
+          <t>-77.602619</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Principal / Calle s / n</t>
+          <t>Avenida Túpac Amaru / Jirón Augusto B Leguia</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,27 +956,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-594257</t>
+          <t>I-57390</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-11.0938163</t>
+          <t>-11.1299197</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-77.5839428</t>
+          <t>-77.6109194</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida San Martin / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-497614</t>
+          <t>I-551253</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-11.0870753</t>
+          <t>-11.1053899</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-77.5718196</t>
+          <t>-77.3152006</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida Libertad / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-439518</t>
+          <t>I-551203</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-11.1974513</t>
+          <t>-11.108692</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-77.4244146</t>
+          <t>-77.3324512</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-57732</t>
+          <t>I-551201</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-11.127642</t>
+          <t>-11.1086151</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-77.614519</t>
+          <t>-77.3327369</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Jose Galvez / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-57390</t>
+          <t>I-498231</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-11.1299197</t>
+          <t>-11.1251544</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-77.6109194</t>
+          <t>-77.6022257</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-498231</t>
+          <t>I-497614</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-11.1251544</t>
+          <t>-11.0870753</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-77.6022257</t>
+          <t>-77.5718196</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Libertad / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-57895</t>
+          <t>I-493573</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-11.1007134</t>
+          <t>-11.0938372</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-77.6211552</t>
+          <t>-77.581623</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>José Olaya / Calle s / n</t>
+          <t>Avenida 28 de Julio / Avenida San Martin</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-57893</t>
+          <t>I-445312</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-11.1017444</t>
+          <t>-11.12715</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-77.6202001</t>
+          <t>-77.6113995</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>José Olaya / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,22 +1332,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-57892</t>
+          <t>I-439880</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-11.1034042</t>
+          <t>-11.214964</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-77.6157061</t>
+          <t>-77.41671</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Jose Olaya / José Olaya / Pasaje Campo Alegre</t>
+          <t>Irrigacion Sta Rosa / 9 De Octubre - Sayan</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-88612</t>
+          <t>I-439878</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-11.2342322</t>
+          <t>-11.216606</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-77.3984911</t>
+          <t>-77.412813</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Irrigacion Santa Rosa / 9 De Octubre - Sayan</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1426,27 +1426,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-88618</t>
+          <t>I-439875</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-11.243499</t>
+          <t>-11.2180889</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-77.4225565</t>
+          <t>-77.409188</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Principal / Calle s / n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-551253</t>
+          <t>I-439518</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-11.1053899</t>
+          <t>-11.1974513</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-77.3152006</t>
+          <t>-77.4244146</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1520,22 +1520,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-551201</t>
+          <t>I-267961</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-11.1086151</t>
+          <t>-11.149087</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-77.3327369</t>
+          <t>-77.24483</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Andahuasi / Sayan</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1567,22 +1567,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-551203</t>
+          <t>I-191372</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-11.108692</t>
+          <t>-11.1042363</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-77.3324512</t>
+          <t>-77.5755234</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida El Milagro / Avenida Libertad</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
